--- a/static/data/exports/Retro_KL_AE_2011.xlsx
+++ b/static/data/exports/Retro_KL_AE_2011.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_KL_AE_2011.xlsx
+++ b/static/data/exports/Retro_KL_AE_2011.xlsx
@@ -9831,20 +9831,20 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1701709</v>
+        <v>1701708</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rashid P.T</t>
+          <t>C.Muneer</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SDPI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>19701</v>
+        <v>19702</v>
       </c>
       <c r="E152" t="n">
         <v>985</v>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Rashid P.T</t>
+          <t>C.Muneer</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>SDPI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q152" t="b">
@@ -9893,20 +9893,20 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1701708</v>
+        <v>1701709</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>C.Muneer</t>
+          <t>Rashid P.T</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SDPI</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>19702</v>
+        <v>19701</v>
       </c>
       <c r="E153" t="n">
         <v>985</v>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>C.Muneer</t>
+          <t>Rashid P.T</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SDPI</t>
         </is>
       </c>
       <c r="Q153" t="b">
